--- a/Excel/EquipGroupConfig.xlsx
+++ b/Excel/EquipGroupConfig.xlsx
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="483">
   <si>
     <t>_id</t>
   </si>
@@ -1514,6 +1514,30 @@
   </si>
   <si>
     <t>1005</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>1050</t>
+  </si>
+  <si>
+    <t>345,345,345</t>
+  </si>
+  <si>
+    <t>1007</t>
+  </si>
+  <si>
+    <t>345,345</t>
+  </si>
+  <si>
+    <t>1008</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>1010</t>
   </si>
 </sst>
 </file>
@@ -2487,7 +2511,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I325"/>
+  <dimension ref="C3:I330"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -8001,9 +8025,94 @@
         <v>471</v>
       </c>
     </row>
+    <row r="326" customHeight="1" spans="3:7">
+      <c r="C326" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="D326" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E326" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F326" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G326" s="5" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="327" customHeight="1" spans="3:7">
+      <c r="C327" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="D327" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E327" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F327" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G327" s="5" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="328" customHeight="1" spans="3:7">
+      <c r="C328" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="D328" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E328" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F328" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G328" s="5" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="329" customHeight="1" spans="3:7">
+      <c r="C329" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D329" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E329" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F329" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G329" s="5" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="330" customHeight="1" spans="3:7">
+      <c r="C330" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="D330" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E330" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F330" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G330" s="5" t="s">
+        <v>479</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 H3 I3 D4 E4 F4 G4 H4 I4 D5 E5 F5:I5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
